--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104675_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104675_W25.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3502</v>
+        <v>5.0017</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2294</v>
+        <v>3.909</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1208</v>
+        <v>1.0927</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8432</v>
+        <v>3.836</v>
       </c>
       <c r="H2" t="n">
-        <v>2.212</v>
+        <v>2.2143</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6312</v>
+        <v>1.6218</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9298</v>
+        <v>3.889</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2614</v>
+        <v>2.244</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6684</v>
+        <v>1.645</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0866</v>
+        <v>-0.053</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3362</v>
+        <v>-0.6734</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1825</v>
+        <v>-0.4533</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1537</v>
+        <v>-0.2201</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.457</v>
+        <v>3.6933</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6443</v>
+        <v>1.3096</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8127</v>
+        <v>2.3838</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5957</v>
+        <v>0.5979</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1241</v>
+        <v>-0.1263</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7197</v>
+        <v>0.7241</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9113</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4289</v>
+        <v>0.4062</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3157</v>
+        <v>-0.2847</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.553</v>
+        <v>-0.5325</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2223</v>
+        <v>0.4612</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2521</v>
+        <v>-0.544</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4744</v>
+        <v>1.0052</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2861</v>
+        <v>3.4073</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3912</v>
+        <v>2.6566</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8949</v>
+        <v>0.7507</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8099</v>
+        <v>1.6347</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2496</v>
+        <v>0.976</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4398</v>
+        <v>0.6587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6169</v>
+        <v>0.7564</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.0862</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3039</v>
+        <v>0.6703</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1929</v>
+        <v>0.8782</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3288</v>
+        <v>0.8898</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1359</v>
+        <v>-0.0116</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1153</v>
+        <v>-1.0892</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4548</v>
+        <v>-0.2788</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6605</v>
+        <v>-0.8104</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.13</v>
+        <v>2.8533</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4567</v>
+        <v>1.4907</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6733</v>
+        <v>1.3625</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6197</v>
+        <v>1.9793</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9666</v>
+        <v>2.2515</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6531</v>
+        <v>-0.2723</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7583</v>
+        <v>1.8182</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0866</v>
+        <v>1.7064</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6717</v>
+        <v>0.1117</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.1611</v>
       </c>
       <c r="N5" t="n">
-        <v>0.88</v>
+        <v>0.5451</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0186</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3556</v>
+        <v>-0.2366</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4869</v>
+        <v>-0.2301</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8686</v>
+        <v>-0.0066</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>2.0212</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0462</v>
+        <v>2.427</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3955</v>
+        <v>2.2495</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6507</v>
+        <v>0.1775</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9682</v>
+        <v>3.9027</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2481</v>
+        <v>1.2858</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2798</v>
+        <v>2.6169</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8263</v>
+        <v>3.6109</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7144</v>
+        <v>0.655</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>2.9559</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1419</v>
+        <v>0.2917</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5337</v>
+        <v>0.6308</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3918</v>
+        <v>-0.3391</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0393</v>
+        <v>-1.0903</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3478</v>
+        <v>-0.2232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3085</v>
+        <v>-0.867</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0246</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5854</v>
+        <v>1.9876</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5968</v>
+        <v>1.185</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0114</v>
+        <v>0.8026</v>
       </c>
       <c r="G7" t="n">
-        <v>3.895</v>
+        <v>0.8088</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2695</v>
+        <v>1.2466</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6255</v>
+        <v>-0.4379</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6353</v>
+        <v>0.5896</v>
       </c>
       <c r="K7" t="n">
-        <v>0.658</v>
+        <v>0.9028</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9772</v>
+        <v>-0.3132</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2598</v>
+        <v>0.2192</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6115</v>
+        <v>0.3438</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3517</v>
+        <v>-0.1246</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.922</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9043</v>
+        <v>0.2783</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0177</v>
+        <v>0.5347</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0947</v>
+        <v>1.2469</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4559</v>
+        <v>-2.7229</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6388</v>
+        <v>3.9698</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3528</v>
+        <v>-2.1384</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9148</v>
+        <v>0.5567</v>
       </c>
       <c r="I8" t="n">
-        <v>1.562</v>
+        <v>-2.6951</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5884</v>
+        <v>-3.4326</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.2276</v>
+        <v>-0.1174</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6392</v>
+        <v>-3.3152</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2356</v>
+        <v>1.2942</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3129</v>
+        <v>0.6741</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0772</v>
+        <v>0.6201</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6847</v>
+        <v>-0.2914</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0484</v>
+        <v>-0.5995</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6364</v>
+        <v>0.3082</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7712</v>
+        <v>4.5871</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>3.8132</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3214</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7379</v>
+        <v>0.9601</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0746</v>
+        <v>0.1637</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8124</v>
+        <v>0.7963</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1053</v>
+        <v>-0.353</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1341</v>
+        <v>-1.9156</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2395</v>
+        <v>1.5626</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1341</v>
+        <v>-0.6143</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8832</v>
+        <v>-2.245</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>1.6308</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2395</v>
+        <v>0.2613</v>
       </c>
       <c r="N9" t="n">
-        <v>0.251</v>
+        <v>0.3294</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4904</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0641</v>
+        <v>-0.8267</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2087</v>
+        <v>-0.3115</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1446</v>
+        <v>-0.5152</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5475</v>
+        <v>0.9262</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9835</v>
+        <v>0.036</v>
       </c>
       <c r="F10" t="n">
-        <v>3.531</v>
+        <v>0.8901</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1387</v>
+        <v>-0.1006</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5482</v>
+        <v>1.1372</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6869</v>
+        <v>-1.2378</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.4084</v>
+        <v>0.1267</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.111</v>
+        <v>0.8791</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.2974</v>
+        <v>-0.7524</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2697</v>
+        <v>-0.2273</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6592</v>
+        <v>0.2581</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6105</v>
+        <v>-0.4854</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.002</v>
+        <v>0.1163</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9043</v>
+        <v>-0.0907</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0977</v>
+        <v>0.2069</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5956</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8243</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7889</v>
+        <v>-1.1599</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3196</v>
+        <v>-1.7283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5684</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1614</v>
+        <v>1.1838</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7588</v>
+        <v>0.7692</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4026</v>
+        <v>0.4146</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8748</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2866</v>
+        <v>0.3194</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1079</v>
+        <v>0.1281</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3841</v>
+        <v>0.0024</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1815</v>
+        <v>-0.1979</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2026</v>
+        <v>0.2003</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7543</v>
+        <v>-1.5961</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6219</v>
+        <v>-1.6274</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1324</v>
+        <v>0.0313</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4463</v>
+        <v>-0.4405</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1428</v>
+        <v>0.1463</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4636</v>
+        <v>-0.4578</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1739</v>
+        <v>-0.0174</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1043</v>
+        <v>0.2614</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.6918</v>
+        <v>19.7474</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1702</v>
+        <v>6.9215</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5215</v>
+        <v>12.8257</v>
       </c>
       <c r="G13" t="n">
-        <v>10.85</v>
+        <v>10.9107</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4908</v>
+        <v>8.541700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.359</v>
+        <v>2.368799999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>8.707300000000002</v>
+        <v>8.508100000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>5.282999999999999</v>
+        <v>5.1755</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4245</v>
+        <v>3.3327</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1425</v>
+        <v>2.402299999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2081</v>
+        <v>3.365899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0654</v>
+        <v>-0.9637999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.4758</v>
+        <v>-12.5197</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.8561</v>
+        <v>-2.8321</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9769</v>
+        <v>-2.9295</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1208</v>
+        <v>0.09739999999999996</v>
       </c>
       <c r="V13" t="n">
-        <v>11.6979</v>
+        <v>11.6686</v>
       </c>
       <c r="W13" t="n">
-        <v>13.9156</v>
+        <v>13.8624</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2177</v>
+        <v>-2.194</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0743</v>
+        <v>4.0246</v>
       </c>
       <c r="E14" t="n">
-        <v>3.336</v>
+        <v>4.0038</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7383</v>
+        <v>0.0208</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3362</v>
+        <v>4.3312</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6365</v>
+        <v>0.6294</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6998</v>
+        <v>3.7018</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0601</v>
+        <v>5.0319</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4404</v>
+        <v>1.4199</v>
       </c>
       <c r="L14" t="n">
-        <v>3.6197</v>
+        <v>3.612</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7239</v>
+        <v>-0.7007</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4186</v>
+        <v>0.3763</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0948</v>
+        <v>-0.386</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5134</v>
+        <v>0.7623</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2793</v>
+        <v>1.387</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.6747</v>
+        <v>1.6475</v>
       </c>
       <c r="F15" t="n">
-        <v>2.954</v>
+        <v>-0.2605</v>
       </c>
       <c r="G15" t="n">
-        <v>1.941</v>
+        <v>-0.4803</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2208</v>
+        <v>1.0142</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2798</v>
+        <v>-1.4945</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3272</v>
+        <v>1.3507</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0016</v>
+        <v>0.9718</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6744</v>
+        <v>0.3789</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6138</v>
+        <v>-1.831</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2192</v>
+        <v>0.0424</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3946</v>
+        <v>-1.8734</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2172</v>
+        <v>0.5016</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5353</v>
+        <v>0.2968</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.2047</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2601</v>
+        <v>0.4494</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5548</v>
+        <v>-2.5946</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8149</v>
+        <v>3.044</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7237</v>
+        <v>1.9424</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7849</v>
+        <v>2.2147</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5087</v>
+        <v>-0.2723</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4251</v>
+        <v>1.3076</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.769</v>
+        <v>1.9855</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1941</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2986</v>
+        <v>0.6349</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0159</v>
+        <v>0.2292</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3145</v>
+        <v>0.4057</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1461</v>
+        <v>0.3995</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2087</v>
+        <v>-0.4163</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0626</v>
+        <v>0.8157</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7712</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7712</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1596</v>
+        <v>0.3496</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5037</v>
+        <v>-0.5639</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6633</v>
+        <v>0.9135</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4645</v>
+        <v>0.7206</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0203</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4848</v>
+        <v>1.5074</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3898</v>
+        <v>0.4192</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9902</v>
+        <v>-0.7724</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3997</v>
+        <v>1.1916</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8543</v>
+        <v>0.3014</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0301</v>
+        <v>-0.0144</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8844</v>
+        <v>0.3159</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0561</v>
+        <v>-0.0523</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8861</v>
+        <v>-0.2091</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.17</v>
+        <v>0.1568</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.285</v>
+        <v>-0.5085</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7309</v>
+        <v>-2.2847</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4459</v>
+        <v>1.7762</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4424</v>
+        <v>-2.1717</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.5264</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>3.084</v>
+        <v>-1.6551</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5642</v>
+        <v>-2.4458</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.7542</v>
+        <v>-0.1142</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3185</v>
+        <v>-2.3317</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0066</v>
+        <v>0.2741</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7721</v>
+        <v>-0.4025</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2345</v>
+        <v>0.6766</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5148</v>
+        <v>-0.0896</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0948</v>
+        <v>-0.3836</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.294</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3278</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4885</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3782</v>
+        <v>-0.882</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8501</v>
+        <v>-1.4191</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4719</v>
+        <v>0.5371</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1634</v>
+        <v>-0.4574</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5107</v>
+        <v>-3.5378</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6526</v>
+        <v>3.0804</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.4225</v>
+        <v>0.5303</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1008</v>
+        <v>-2.7761</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.3218</v>
+        <v>3.3064</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2592</v>
+        <v>-0.9877</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4099</v>
+        <v>-0.7617</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6691</v>
+        <v>-0.226</v>
       </c>
       <c r="P19" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9615</v>
+        <v>-0.0977</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9739</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0124</v>
+        <v>0.6437</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3856</v>
+        <v>-0.3268</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.4846</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6415</v>
+        <v>-3.0913</v>
       </c>
       <c r="E20" t="n">
-        <v>2.281</v>
+        <v>-1.5031</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.9226</v>
+        <v>-1.5882</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9705</v>
+        <v>-3.4811</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.867</v>
+        <v>-1.6026</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1035</v>
+        <v>-1.8785</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0679</v>
+        <v>-0.959</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1425</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-0.276</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9026</v>
+        <v>-2.5221</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7245</v>
+        <v>-0.9196</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1781</v>
+        <v>-1.6025</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9347</v>
+        <v>0.4678</v>
       </c>
       <c r="T20" t="n">
-        <v>2.0294</v>
+        <v>0.6639</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.1961</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.0595</v>
+        <v>0.6049</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.6058</v>
+        <v>0.4471</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6971</v>
+        <v>-3.2746</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2439</v>
+        <v>-2.9467</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4532</v>
+        <v>-0.3279</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4782</v>
+        <v>-0.9917</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6017</v>
+        <v>-2.3233</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8765</v>
+        <v>1.3315</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9389</v>
+        <v>-0.9487</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6722</v>
+        <v>-1.2313</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2666</v>
+        <v>0.2826</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5393</v>
+        <v>-0.043</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9294</v>
+        <v>-1.092</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6099</v>
+        <v>1.049</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8574000000000001</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8953</v>
+        <v>-0.6322</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0378</v>
+        <v>0.538</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6041</v>
+        <v>-1.9611</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.4434</v>
+        <v>-1.9611</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8422</v>
+        <v>-3.3632</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.435</v>
+        <v>-0.91</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4072</v>
+        <v>-2.4532</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6248</v>
+        <v>-0.6233</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.153</v>
+        <v>-0.1495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4718</v>
+        <v>-0.4738</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="K22" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4482</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2994</v>
+        <v>-0.1721</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1488</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8791</v>
+        <v>-3.6048</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6802</v>
+        <v>-2.4709</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1989</v>
+        <v>-1.1338</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-2.0238</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3188</v>
+        <v>-0.8129</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3354</v>
+        <v>-1.2109</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.923</v>
+        <v>-1.7271</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2162</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2931</v>
+        <v>-0.8718</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0603</v>
+        <v>-0.2967</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1026</v>
+        <v>0.0424</v>
       </c>
       <c r="O23" t="n">
-        <v>1.0423</v>
+        <v>-0.3391</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2979</v>
+        <v>0.598</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3962</v>
+        <v>0.3943</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.2036</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.9668</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9668</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0906</v>
+        <v>-3.722</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4531</v>
+        <v>1.0834</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6375</v>
+        <v>-4.8054</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.0308</v>
+        <v>-1.9801</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8153</v>
+        <v>-0.881</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2154</v>
+        <v>-1.0991</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7091</v>
+        <v>-0.0881</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8454</v>
+        <v>-0.1626</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8637</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3216</v>
+        <v>-1.892</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0301</v>
+        <v>-0.7184</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3517</v>
+        <v>-1.1736</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1255</v>
+        <v>0.8534</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3902</v>
+        <v>0.8545</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2646</v>
+        <v>-0.0011</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-3.0505</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-3.5953</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3322</v>
+        <v>-6.466</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0195</v>
+        <v>-4.8673</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3127</v>
+        <v>-1.5987</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.6931</v>
+        <v>-5.6953</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7907</v>
+        <v>-1.7894</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.9024</v>
+        <v>-3.9059</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.1133</v>
+        <v>-4.1352</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1917</v>
+        <v>-1.2001</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.9215</v>
+        <v>-2.9351</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5798</v>
+        <v>-1.5601</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2351</v>
+        <v>1.1009</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4548</v>
+        <v>0.6337</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7803</v>
+        <v>0.4672</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.6918</v>
+        <v>-18.7018</v>
       </c>
       <c r="E26" t="n">
-        <v>-12.5215</v>
+        <v>-12.8256</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.170399999999999</v>
+        <v>-5.876099999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-10.8502</v>
+        <v>-10.9105</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.4909</v>
+        <v>-8.541599999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.3589</v>
+        <v>-2.368999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.1427</v>
+        <v>-2.402099999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.2078</v>
+        <v>-3.366099999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>1.065299999999999</v>
+        <v>0.9639000000000002</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.7072</v>
+        <v>-8.5083</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.282900000000001</v>
+        <v>-5.1757</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.4244</v>
+        <v>-3.3325</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="Q26" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8561</v>
+        <v>3.8777</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1206999999999998</v>
+        <v>-0.09749999999999959</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9771</v>
+        <v>3.9748</v>
       </c>
       <c r="V26" t="n">
-        <v>-11.698</v>
+        <v>-11.6684</v>
       </c>
       <c r="W26" t="n">
-        <v>2.2176</v>
+        <v>2.1939</v>
       </c>
       <c r="X26" t="n">
-        <v>-13.9156</v>
+        <v>-13.8625</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104675_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104675_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-2.194</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.4846</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.4471</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.9611</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.5953</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104675_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-13.8625</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
